--- a/FLORES DE ESTRADA/Junio/RESUMEN-JUNIO-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Junio/RESUMEN-JUNIO-ESTRADA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FC712B-9E63-4F0A-A413-EBDF204F92FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3375A069-E814-45D7-A811-609A1E2A31B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$54</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -141,12 +141,6 @@
     <t>CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES FUNCIONALES ATRASADAS. QUIEN SE ATRASE CON EDESUR TENDRA PUNITORIOS.</t>
   </si>
   <si>
-    <t>Servisur - mano de obra instalacion reflector</t>
-  </si>
-  <si>
-    <t>Casa ruan compra de reflector, dicroicas y cable unipolar</t>
-  </si>
-  <si>
     <t>PERIODO: JUNIO - Vto. 14/07</t>
   </si>
   <si>
@@ -166,6 +160,9 @@
   </si>
   <si>
     <t>Julio Doartero - Arreglo porton 13/06</t>
+  </si>
+  <si>
+    <t>SAC</t>
   </si>
 </sst>
 </file>
@@ -178,7 +175,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,13 +253,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -460,7 +450,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -488,8 +478,6 @@
     <xf numFmtId="165" fontId="7" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -517,12 +505,6 @@
     <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -581,7 +563,8 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -919,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
@@ -929,20 +912,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
+      <c r="A2" s="26"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="31" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -953,10 +936,10 @@
       <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="31" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="11">
@@ -967,13 +950,13 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="32" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="11"/>
@@ -981,10 +964,10 @@
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="31" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="11"/>
@@ -993,7 +976,7 @@
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -1003,31 +986,31 @@
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="34"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
@@ -1041,7 +1024,7 @@
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -1065,19 +1048,19 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="26" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="11"/>
@@ -1086,123 +1069,124 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="39">
+      <c r="H13" s="37">
         <v>194000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="63" t="s">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="37">
+        <f>H13/2</f>
+        <v>97000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="39">
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="37">
         <v>3567.21</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42">
-        <f>SUM(H13:H14)</f>
-        <v>197567.21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="60" t="s">
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40">
+        <f>SUM(H13:H15)</f>
+        <v>294567.21000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="62"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="72">
-        <v>29428.15</v>
-      </c>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="58"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="41">
+        <v>28837.360000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="44">
-        <f>SUM(H17:H17)</f>
-        <v>29428.15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="60" t="s">
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="42">
+        <f>SUM(H18:H18)</f>
+        <v>28837.360000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="62"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="45" t="s">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="58"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47">
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
         <v>32</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>9</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1210,289 +1194,287 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
-      <c r="H22" s="48">
-        <f>SUM(H20:H21)</f>
+      <c r="H22" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="46">
+        <f>SUM(H21:H22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="65" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="43">
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="41">
         <v>91930.94</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="43">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="43">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="72">
+    <row r="26" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="41">
         <v>115000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="44">
-        <f>SUM(H24:H27)</f>
-        <v>263430.94</v>
-      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="42">
+        <f>SUM(H25:H26)</f>
+        <v>206930.94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="58"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
+      <c r="A29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="26"/>
+      <c r="A30" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="48">
+        <v>139770.16</v>
+      </c>
+      <c r="I30" s="24"/>
+      <c r="K30" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="52">
-        <v>139770.16</v>
-      </c>
-      <c r="I31" s="26"/>
-      <c r="K31" t="s">
-        <v>35</v>
-      </c>
+      <c r="A31" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="59"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="49">
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="47">
         <v>49773</v>
       </c>
     </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="10">
+        <f>H32+H30+H27+H23+H19+H16</f>
+        <v>719878.66999999993</v>
+      </c>
+    </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="10">
-        <f>H33+H31+H28+H22+H18+H15</f>
-        <v>679969.46</v>
-      </c>
+      <c r="A34" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="68"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="22">
-        <v>500000</v>
+      <c r="A35" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="69">
+        <f>H33+H34</f>
+        <v>719878.66999999993</v>
       </c>
       <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="22">
-        <f>H34+H35</f>
-        <v>1179969.46</v>
-      </c>
-      <c r="I36" s="29"/>
-    </row>
-    <row r="37" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="69" t="str">
+    </row>
+    <row r="36" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="65" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="53">
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="49">
         <v>700000</v>
       </c>
     </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+    </row>
     <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="55"/>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+    </row>
+    <row r="40" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="52"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="54"/>
+      <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="58"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="12" t="s">
+      <c r="A41" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="20">
-        <v>1495376.39</v>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="20">
+        <v>1957831.0783125074</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="22">
+        <v>1398149.0448363998</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -1500,13 +1482,12 @@
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
-      <c r="H43" s="24">
-        <v>1264656.6683125077</v>
-      </c>
+      <c r="H43" s="16"/>
+      <c r="I43" s="23"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -1514,12 +1495,14 @@
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="25"/>
+      <c r="H44" s="17">
+        <f>-( H33 )</f>
+        <v>-719878.66999999993</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -1527,125 +1510,110 @@
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
-      <c r="H45" s="17">
-        <f>-( H34 )</f>
-        <v>-679969.46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="17"/>
-    </row>
-    <row r="47" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
+      <c r="H45" s="17"/>
+    </row>
+    <row r="46" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="23">
-        <f>SUM(H42:H46)</f>
-        <v>2080063.5983125074</v>
-      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="21">
+        <f>SUM(H41:H45)</f>
+        <v>2636101.4531489071</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
+      <c r="B48" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
       <c r="H48" s="11"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
-      <c r="B49" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
       <c r="H49" s="11"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
+      <c r="B50" s="50"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
+      <c r="G50" s="50"/>
       <c r="H50" s="11"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
       <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
       <c r="H52" s="11"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="54"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50"/>
+      <c r="E53" s="50"/>
+      <c r="F53" s="50"/>
+      <c r="G53" s="50"/>
       <c r="H53" s="11"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="11"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="54"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B49:G54"/>
-    <mergeCell ref="A38:H39"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="B48:G53"/>
+    <mergeCell ref="A37:H38"/>
+    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
